--- a/tests/scen_results_AGO.xlsx
+++ b/tests/scen_results_AGO.xlsx
@@ -27,7 +27,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-04-24</t>
+    <t>2025-04-28</t>
   </si>
   <si>
     <t>Scenario</t>
